--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488100_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488100_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.916</v>
+        <v>2.5729</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9832</v>
+        <v>5.6963</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0672</v>
+        <v>-3.1234</v>
       </c>
       <c r="G2" t="n">
         <v>4.3674</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6491</v>
+        <v>-0.9922</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7891</v>
+        <v>-0.076</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.86</v>
+        <v>-0.9161</v>
       </c>
       <c r="V2" t="n">
         <v>1.3781</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2053</v>
+        <v>1.4682</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2053</v>
+        <v>1.9352</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.467</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2053</v>
+        <v>0.7135</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.505</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2053</v>
+        <v>1.2185</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2053</v>
+        <v>1.6084</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.2825</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2053</v>
+        <v>1.3259</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.8948</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.7875</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.1073</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.3069</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.3268</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1.6337</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1811</v>
+        <v>1.2173</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8728</v>
+        <v>0.5522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6916</v>
+        <v>0.6651</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7135</v>
+        <v>0.3819</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.505</v>
+        <v>-0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2185</v>
+        <v>0.4228</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6084</v>
+        <v>0.1451</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2825</v>
+        <v>0.1412</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3259</v>
+        <v>0.0039</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8948</v>
+        <v>0.2367</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7875</v>
+        <v>-0.1822</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1073</v>
+        <v>0.4189</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5939</v>
+        <v>-0.4222</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2644</v>
+        <v>0.1405</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8583</v>
+        <v>-0.5627</v>
       </c>
       <c r="V4" t="n">
-        <v>0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0041</v>
+        <v>1.2053</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5917</v>
+        <v>1.2053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4124</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3819</v>
+        <v>1.2053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0409</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4228</v>
+        <v>1.2053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1451</v>
+        <v>1.2053</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1412</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0039</v>
+        <v>1.2053</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2367</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1822</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4189</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6355</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8154</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>A. GUTIERREZ MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3408</v>
+        <v>-0.2999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1913</v>
+        <v>0.1019</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.532</v>
+        <v>-0.4018</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0252</v>
+        <v>-0.266</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="U7" t="n">
         <v>-0.1358</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.1107</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.1252</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.9243</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.2009</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-2.1504</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-2.0602</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.0902</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-3.7662</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-5.9467</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.7355</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.6689</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.9334</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.7151</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3438</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4018</v>
+        <v>-0.2999</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
       <c r="F8" t="n">
         <v>-0.4018</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1358</v>
+        <v>-0.034</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1358</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MORENO</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4018</v>
+        <v>-2.0663</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.4781</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4018</v>
+        <v>-1.5882</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.266</v>
+        <v>-0.0252</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.1358</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.266</v>
+        <v>0.1107</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.1252</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.9243</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.2009</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.266</v>
+        <v>-2.1504</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-2.0602</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.266</v>
+        <v>-0.0902</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-3.7662</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-5.9467</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1358</v>
+        <v>0.01</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.9996</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1358</v>
+        <v>-0.9896</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.7151</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3438</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6287</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7809</v>
+        <v>-3.62</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8518</v>
+        <v>-2.1574</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9291</v>
+        <v>-1.4626</v>
       </c>
       <c r="G10" t="n">
         <v>-2.066</v>
@@ -1234,13 +1234,13 @@
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4224</v>
+        <v>-0.4167</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6095</v>
+        <v>0.3039</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1871</v>
+        <v>-0.7206</v>
       </c>
       <c r="V10" t="n">
         <v>0.845</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2471</v>
+        <v>-3.8967</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2924</v>
+        <v>-1.0263</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9546</v>
+        <v>-2.8704</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8459</v>
@@ -1312,13 +1312,13 @@
         <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6692</v>
+        <v>-1.3189</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5068</v>
+        <v>0.7729</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.176</v>
+        <v>-2.0918</v>
       </c>
       <c r="V11" t="n">
         <v>1.4485</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0216</v>
+        <v>-4.8459</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8335</v>
+        <v>-2.6297</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1881</v>
+        <v>-2.2162</v>
       </c>
       <c r="G12" t="n">
         <v>0.0873</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9805</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0552</v>
+        <v>0.2589</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0357</v>
+        <v>-1.0638</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3621</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.3987</v>
+        <v>-9.409000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1608</v>
+        <v>-4.2834</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.2379</v>
+        <v>-5.1256</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7371</v>
@@ -1468,13 +1468,13 @@
         <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.058</v>
+        <v>-1.0683</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5395</v>
+        <v>0.3378</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5185</v>
+        <v>-1.4062</v>
       </c>
       <c r="V13" t="n">
         <v>-4.2249</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.9835</v>
+        <v>-17.6713</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9914999999999985</v>
+        <v>-0.6794000000000016</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.9917</v>
+        <v>-16.9919</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8519000000000003</v>
+        <v>0.8518999999999994</v>
       </c>
       <c r="H14" t="n">
         <v>-1.2994</v>
@@ -1546,13 +1546,13 @@
         <v>11.8934</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.6999</v>
+        <v>-6.3881</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9562</v>
+        <v>3.268200000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.655999999999999</v>
+        <v>-9.6561</v>
       </c>
       <c r="V14" t="n">
         <v>1.7403</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.1912</v>
+        <v>6.9891</v>
       </c>
       <c r="E15" t="n">
-        <v>7.279</v>
+        <v>6.3622</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9122</v>
+        <v>0.6268</v>
       </c>
       <c r="G15" t="n">
         <v>4.8879</v>
@@ -1624,13 +1624,13 @@
         <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>2.777</v>
+        <v>1.5748</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9788</v>
+        <v>1.062</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7982</v>
+        <v>0.5129</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2666</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5917</v>
+        <v>3.8001</v>
       </c>
       <c r="E16" t="n">
-        <v>3.328</v>
+        <v>2.5012</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2638</v>
+        <v>1.2989</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2474</v>
+        <v>2.553</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.278</v>
+        <v>-0.097</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0306</v>
+        <v>2.6499</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3365</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8549</v>
+        <v>-0.5782</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5184</v>
+        <v>2.3783</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5839</v>
+        <v>0.7529</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1329</v>
+        <v>0.4813</v>
       </c>
       <c r="O16" t="n">
-        <v>0.549</v>
+        <v>0.2717</v>
       </c>
       <c r="P16" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9733</v>
+        <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>3.304</v>
+        <v>0.2561</v>
       </c>
       <c r="T16" t="n">
-        <v>3.7666</v>
+        <v>0.7012</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4626</v>
+        <v>-0.4451</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8448</v>
+        <v>3.4864</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6863</v>
+        <v>1.0868</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1585</v>
+        <v>2.3996</v>
       </c>
       <c r="G17" t="n">
-        <v>2.553</v>
+        <v>-0.2474</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.097</v>
+        <v>-0.278</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6499</v>
+        <v>0.0306</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>0.3365</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5782</v>
+        <v>0.8549</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3783</v>
+        <v>-0.5184</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7529</v>
+        <v>-0.5839</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4813</v>
+        <v>-1.1329</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2717</v>
+        <v>0.549</v>
       </c>
       <c r="P17" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>2.9733</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6993</v>
+        <v>1.1986</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1138</v>
+        <v>1.5255</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5855</v>
+        <v>-0.3268</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7034</v>
+        <v>3.098</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8113</v>
+        <v>3.5214</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8922</v>
+        <v>-0.4234</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9707</v>
+        <v>3.7834</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3287</v>
+        <v>4.4568</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2995</v>
+        <v>-0.6734</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0752</v>
+        <v>5.0351</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9843</v>
+        <v>5.5898</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9091</v>
+        <v>-0.5547</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.046</v>
+        <v>-1.2517</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6556</v>
+        <v>-1.1329</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3904</v>
+        <v>-0.1187</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9822</v>
+        <v>0.3964</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8922</v>
+        <v>0.3919</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9274</v>
+        <v>0.202</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0352</v>
+        <v>0.1899</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7997</v>
+        <v>-1.4737</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7997</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.255</v>
+        <v>2.9503</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7065</v>
+        <v>1.5057</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4514</v>
+        <v>1.4446</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7834</v>
+        <v>-0.9707</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4568</v>
+        <v>1.3287</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6734</v>
+        <v>-2.2995</v>
       </c>
       <c r="J19" t="n">
-        <v>5.0351</v>
+        <v>0.0752</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5898</v>
+        <v>1.9843</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5547</v>
+        <v>-1.9091</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2517</v>
+        <v>-1.046</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1329</v>
+        <v>-0.6556</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1187</v>
+        <v>-0.3904</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3964</v>
+        <v>1.9822</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4512</v>
+        <v>1.139</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6129</v>
+        <v>1.6218</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1618</v>
+        <v>-0.4828</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4737</v>
+        <v>0.7997</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0.7997</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4886</v>
+        <v>1.2685</v>
       </c>
       <c r="E21" t="n">
-        <v>2.881</v>
+        <v>2.4735</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3924</v>
+        <v>-1.205</v>
       </c>
       <c r="G21" t="n">
         <v>-2.87</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2287</v>
+        <v>1.0086</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5492</v>
+        <v>1.1418</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3206</v>
+        <v>-0.1332</v>
       </c>
       <c r="V21" t="n">
         <v>1.5441</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3882</v>
+        <v>0.3823</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1808</v>
+        <v>-0.4864</v>
       </c>
       <c r="F25" t="n">
-        <v>0.569</v>
+        <v>0.8687</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1047</v>
@@ -2404,13 +2404,13 @@
         <v>2.3787</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1142</v>
+        <v>0.1083</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7343</v>
+        <v>0.4287</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6201</v>
+        <v>-0.3203</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6357</v>
+        <v>0.1342</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1998</v>
+        <v>-2.0248</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.8354</v>
+        <v>2.159</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6923</v>
+        <v>-0.8488</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.7933</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6141</v>
+        <v>-0.0555</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5593</v>
+        <v>0.271</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5114</v>
+        <v>0.3436</v>
       </c>
       <c r="L26" t="n">
-        <v>0.048</v>
+        <v>-0.0726</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2517</v>
+        <v>-1.1198</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5896</v>
+        <v>-1.1369</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.662</v>
+        <v>0.0171</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1805</v>
+        <v>2.7751</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3835</v>
+        <v>0.19</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4333</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8169</v>
+        <v>0.0963</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2071</v>
+        <v>-0.4074</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.9474</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.1281</v>
+        <v>-0.1897</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.0435</v>
+        <v>2.5054</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9154</v>
+        <v>-2.695</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8488</v>
+        <v>-0.6923</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7933</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0555</v>
+        <v>-0.6141</v>
       </c>
       <c r="J27" t="n">
-        <v>0.271</v>
+        <v>0.5593</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3436</v>
+        <v>0.5114</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.0726</v>
+        <v>0.048</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1198</v>
+        <v>-1.2517</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.1369</v>
+        <v>-0.5896</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0171</v>
+        <v>-0.662</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7751</v>
+        <v>2.1805</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0722</v>
+        <v>0.0625</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0.7389</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1473</v>
+        <v>-0.6765</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.4074</v>
+        <v>1.2071</v>
       </c>
       <c r="X27" t="n">
-        <v>0.4074</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>M. LOPEZ PERAGON</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,73 +2593,73 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.5843</v>
+        <v>-0.948</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3755</v>
+        <v>-0.9705</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2088</v>
+        <v>0.0225</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.113</v>
+        <v>-2.7114</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.0551</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.0578</v>
+        <v>-1.9609</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.1098</v>
+        <v>-1.7956</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.3179</v>
+        <v>0.0409</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.7919</v>
+        <v>-1.8365</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.0032</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.7372</v>
+        <v>-0.7914</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.266</v>
+        <v>-0.1244</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5375</v>
+        <v>1.2986</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7343</v>
+        <v>1.3336</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1968</v>
+        <v>-0.035</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>M. LOPEZ PERAGON</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.7172</v>
+        <v>-1.7776</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.6836</v>
+        <v>-1.6811</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0336</v>
+        <v>-0.0965</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.7114</v>
+        <v>-3.113</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-2.0551</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.9609</v>
+        <v>-1.0578</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.7956</v>
+        <v>-2.1098</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0409</v>
+        <v>-1.3179</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.8365</v>
+        <v>-0.7919</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.0032</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.7914</v>
+        <v>-0.7372</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.1244</v>
+        <v>-0.266</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5294</v>
+        <v>0.3442</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.4287</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.0911</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V29" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.3356</v>
+        <v>-3.7734</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.5378</v>
+        <v>-1.7229</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.7978</v>
+        <v>-2.0505</v>
       </c>
       <c r="G30" t="n">
         <v>-2.4393</v>
@@ -2794,13 +2794,13 @@
         <v>1.5858</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4855</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.4368</v>
+        <v>0.3782</v>
       </c>
       <c r="U30" t="n">
-        <v>0.36</v>
+        <v>0.1073</v>
       </c>
       <c r="V30" t="n">
         <v>-2.4142</v>
@@ -2827,22 +2827,22 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>17.9833</v>
+        <v>19.3415</v>
       </c>
       <c r="E31" t="n">
-        <v>16.992</v>
+        <v>16.9918</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9916999999999994</v>
+        <v>2.349699999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8519999999999994</v>
+        <v>-0.8520000000000003</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2995</v>
+        <v>1.299500000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.1515</v>
+        <v>-2.151500000000001</v>
       </c>
       <c r="J31" t="n">
         <v>11.6645</v>
@@ -2851,13 +2851,13 @@
         <v>10.5916</v>
       </c>
       <c r="L31" t="n">
-        <v>1.0733</v>
+        <v>1.073299999999999</v>
       </c>
       <c r="M31" t="n">
         <v>-12.5167</v>
       </c>
       <c r="N31" t="n">
-        <v>-9.291900000000002</v>
+        <v>-9.2919</v>
       </c>
       <c r="O31" t="n">
         <v>-3.2246</v>
@@ -2872,13 +2872,13 @@
         <v>25.769</v>
       </c>
       <c r="S31" t="n">
-        <v>6.699999999999998</v>
+        <v>8.0581</v>
       </c>
       <c r="T31" t="n">
-        <v>9.655999999999999</v>
+        <v>9.656200000000002</v>
       </c>
       <c r="U31" t="n">
-        <v>-2.9561</v>
+        <v>-1.5978</v>
       </c>
       <c r="V31" t="n">
         <v>-1.7403</v>
